--- a/task-reviews/charts/task_charts_counting_value_count/task_charts_counting_value_count.xlsx
+++ b/task-reviews/charts/task_charts_counting_value_count/task_charts_counting_value_count.xlsx
@@ -4285,31 +4285,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Determine how many marks show values strictly greater than 8.
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 4?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 4?
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Determine how many marks show values strictly greater than 8.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["F", "R", "T", "Y"], "answer": 4}</t>
+          <t>{"evidence": ["M", "P", "R", "S", "T", "X", "Y", "Z"], "answer": 8}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["F", "R", "T", "Y"]</t>
+          <t>["M", "P", "R", "S", "T", "X", "Y", "Z"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4323,16 +4323,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>51524045199251</v>
+        <v>505904538338456</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0010.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0012.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0010.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0012.json</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values higher than 4?
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 0.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer: set "answer" to the number of matching marks as an integer.
@@ -4359,21 +4359,21 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values higher than 4?
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 0.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
+Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["D", "E", "P", "T", "Z"], "answer": 5}</t>
+          <t>{"evidence": ["B", "F", "J", "M", "P", "T", "W", "X"], "answer": 8}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["D", "E", "P", "T", "Z"]</t>
+          <t>["B", "F", "J", "M", "P", "T", "W", "X"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>274927673375540</v>
+        <v>520251065966359</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0023.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0015.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0023.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0015.json</t>
         </is>
       </c>
     </row>
@@ -4413,31 +4413,31 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values above 12.
+          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 4.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values above 12.
+          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 4.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "C", "D", "F", "J", "L", "P", "X", "Y"], "answer": 9}</t>
+          <t>{"evidence": ["J", "S"], "answer": 2}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["B", "C", "D", "F", "J", "L", "P", "X", "Y"]</t>
+          <t>["J", "S"]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4451,16 +4451,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>338557379373401</v>
+        <v>642723237711261</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0007.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0018.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0007.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0018.json</t>
         </is>
       </c>
     </row>
@@ -4477,17 +4477,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 8.
+          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 13?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
+Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 8.
+          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 13?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
@@ -4496,12 +4496,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["U", "Y"], "answer": 2}</t>
+          <t>{"evidence": ["F", "J", "K", "N", "Y"], "answer": 5}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>["U", "Y"]</t>
+          <t>["F", "J", "K", "N", "Y"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4515,16 +4515,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>772197109336267</v>
+        <v>1022472862598886</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0000.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0003.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0000.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0003.json</t>
         </is>
       </c>
     </row>
@@ -4541,17 +4541,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 7?
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. What number of labeled marks have values higher than 22?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 7?
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. What number of labeled marks have values higher than 22?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
@@ -4560,12 +4560,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "H", "M", "R", "S"], "answer": 5}</t>
+          <t>{"evidence": ["E", "K", "Z"], "answer": 3}</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>["E", "H", "M", "R", "S"]</t>
+          <t>["E", "K", "Z"]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4579,16 +4579,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>905577208865466</v>
+        <v>1345450068782110</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0022.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0017.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0022.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0017.json</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Count the labeled marks with values above 17.
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 7.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -4615,7 +4615,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Count the labeled marks with values above 17.
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 7.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
@@ -4624,12 +4624,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [], "answer": 0}</t>
+          <t>{"evidence": ["V"], "answer": 1}</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["V"]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4643,16 +4643,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1117441605598584</v>
+        <v>1383118390360517</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0020.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0009.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0020.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0009.json</t>
         </is>
       </c>
     </row>
@@ -4669,31 +4669,31 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 5?
+          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 19.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 5?
+          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks exceed 19.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
+Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["F", "G"], "answer": 2}</t>
+          <t>{"evidence": ["J", "K", "Q", "R"], "answer": 4}</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>["F", "G"]</t>
+          <t>["J", "K", "Q", "R"]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4707,16 +4707,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1190228086579991</v>
+        <v>1920644884103717</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0017.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0000.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0017.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0000.json</t>
         </is>
       </c>
     </row>
@@ -4733,31 +4733,31 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 3?
+          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Find how many labeled marks exceed 1.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Find how many labeled marks exceed 1.
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 3?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["H"], "answer": 1}</t>
+          <t>{"evidence": ["G", "H", "J", "T", "W", "X", "Z"], "answer": 7}</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>["H"]</t>
+          <t>["G", "H", "J", "T", "W", "X", "Z"]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1773714674166442</v>
+        <v>2000287209370783</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0006.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0004.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0006.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0004.json</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 18?
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. How many labeled marks have value greater than 0?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -4807,21 +4807,21 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 18?
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. How many labeled marks have value greater than 0?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
+Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "C", "H", "N", "V", "Y"], "answer": 6}</t>
+          <t>{"evidence": ["C", "J", "L", "R", "X", "Y"], "answer": 6}</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>["B", "C", "H", "N", "V", "Y"]</t>
+          <t>["C", "J", "L", "R", "X", "Y"]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4835,16 +4835,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1948510501958545</v>
+        <v>2133129878743127</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0012.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0019.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0012.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0019.json</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,711 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks have values higher than 0?
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 15?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 15?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["E"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2820291246570642</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0021.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="216.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Determine how many marks show values strictly greater than 3.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Determine how many marks show values strictly greater than 3.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "J", "K", "Q"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["A", "J", "K", "Q"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3195949957727500</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0007.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="216.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks have values higher than 18?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks have values higher than 18?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D", "L", "S", "Z"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["D", "L", "S", "Z"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3538541189172507</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0006.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="216.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value greater than 27?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value greater than 27?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["P"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>["P"]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3616058431003272</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0014.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="216.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 19.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 19.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3664497987736641</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0005.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="216.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks with values above 15.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks with values above 15.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["L", "R", "V", "W", "X"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["L", "R", "V", "W", "X"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4088696915252599</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0024.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="216.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 14.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 14.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["G", "J", "N", "W", "Z"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>["G", "J", "N", "W", "Z"]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5026729626272233</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0020.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="216.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values above 2.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values above 2.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E", "K", "N", "Y"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["E", "K", "N", "Y"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5424825578941056</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0013.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="216.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values higher than 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["F", "N", "T", "U", "V", "Y", "Z"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["F", "N", "T", "U", "V", "Y", "Z"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5846711302074502</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0011.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="216.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Find how many labeled marks exceed 15.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Find how many labeled marks exceed 15.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["C"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6688185684742873</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0023.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="216.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values higher than 8?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["B","K","T"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values higher than 8?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "T", "V"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["C", "T", "V"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6744749301374069</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0022.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="216.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks with values above 19.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer: set "answer" to the number of matching marks as an integer.
@@ -4869,63 +5573,63 @@
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks have values higher than 0?
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks with values above 19.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["E", "G", "H", "M", "N", "Q", "S", "X", "Z"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>["E", "G", "H", "M", "N", "Q", "S", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>3915055070466993</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0001.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0001.json</t>
+      <c r="K22" t="n">
+        <v>6836386259295877</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0016.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="216.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="23" ht="216.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>above_threshold</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 3?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 15?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -4933,447 +5637,63 @@
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 3?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "C", "F", "G", "K", "L", "Q", "T"], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>["A", "C", "F", "G", "K", "L", "Q", "T"]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3935832533111039</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0002.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="216.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Count the labeled marks with values above 17.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Count the labeled marks with values above 17.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["Q", "R"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>["Q", "R"]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4604470801383472</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0004.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="216.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values higher than 15?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values higher than 15?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["Q", "T"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>["Q", "T"]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4903303067777680</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0005.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="216.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value greater than 11?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value greater than 11?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["G", "M", "R", "U", "X", "Z"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>["G", "M", "R", "U", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5317069790836089</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0009.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Find how many labeled marks exceed 62.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Find how many labeled marks exceed 62.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["T"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>["T"]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5715911179738960</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0021.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="216.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Find how many labeled marks exceed 3.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Find how many labeled marks exceed 3.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value greater than 15?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "D", "H", "K", "L", "N", "R", "Y", "Z"], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "D", "H", "K", "L", "N", "R", "Y", "Z"]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["L", "M"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["L", "M"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>5792132300337997</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0014.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0014.json</t>
+      <c r="K23" t="n">
+        <v>7044630367047802</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0008.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="216.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
+    <row r="24" ht="216.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>above_threshold</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Find how many labeled marks exceed 1.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Find how many labeled marks exceed 1.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "S", "Y"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>["C", "S", "Y"]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6114853329186159</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0008.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="216.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 10?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Answer this question. Find how many labeled marks exceed 1.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer: set "answer" to the number of matching marks as an integer.
@@ -5381,63 +5701,63 @@
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Determine how many labeled marks meet the stated value condition. How many labeled marks have value greater than 10?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Answer this question. Find how many labeled marks exceed 1.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
+Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["J", "R", "U", "Y"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>["J", "R", "U", "Y"]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "G", "H", "P", "Q", "T", "U", "W", "X"], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "G", "H", "P", "Q", "T", "U", "W", "X"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>6410096074616141</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0018.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0018.json</t>
+      <c r="K24" t="n">
+        <v>7486374244778465</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0001.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="216.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
+    <row r="25" ht="216.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>above_threshold</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 13.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 16.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -5445,63 +5765,63 @@
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values above 13.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 16.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
+Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "E", "S", "X"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>["C", "E", "S", "X"]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["U"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["U"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>6463702802502175</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0024.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0024.json</t>
+      <c r="K25" t="n">
+        <v>7937173686730022</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0010.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="216.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
+    <row r="26" ht="216.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>above_threshold</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values above 4.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 80.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -5509,366 +5829,46 @@
 {"evidence":["B","K","T"],"answer":3}</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values above 4.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly greater than 80.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
+Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "E", "L", "M", "N", "X", "Y"], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>["B", "E", "L", "M", "N", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>6705074145867633</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0013.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="216.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Answer this question. How many labeled marks have value greater than 17?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Answer this question. How many labeled marks have value greater than 17?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "D", "M", "N", "T"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>["B", "D", "M", "N", "T"]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7039867810456558</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0015.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="216.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value greater than 5?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value greater than 5?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "D", "G", "H", "J", "K", "L", "N", "R", "U"], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>["C", "D", "G", "H", "J", "K", "L", "N", "R", "U"]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>7749722507509282</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0016.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="216.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Find how many labeled marks exceed 18.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Find how many labeled marks exceed 18.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "D", "F", "T", "U"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "D", "F", "T", "U"]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8544672399434556</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0019.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="216.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values higher than 4?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values higher than 4?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "G", "K", "L", "W", "X"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>["C", "G", "K", "L", "W", "X"]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8867904069595298</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0011.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="216.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>above_threshold</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly greater than 5.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values greater than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["B","K","T"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly greater than 5.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["G", "J", "M", "X", "Y"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>["G", "J", "M", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8878090650335808</v>
+        <v>8452438338833501</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/above_threshold/0003.png</t>
+          <t>charts/task_charts_counting_value_count/images/above_threshold/0002.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/above_threshold/0003.json</t>
+          <t>charts/task_charts_counting_value_count/data/above_threshold/0002.json</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Find how many labeled marks are under 3.
+          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly less than 18.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly less than 18.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "E", "V", "X", "Z"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>["C", "E", "V", "X", "Z"]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>179901532196556</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0023.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="216.75" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 2.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 2.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>["D"]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>206667917396907</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0009.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="216.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Find how many labeled marks are under 9.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Find how many labeled marks are under 9.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["H"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>["H"]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>561625463455636</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0015.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="216.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 13.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -5990,63 +6182,191 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Find how many labeled marks are under 3.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 13.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["J"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>["J"]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["S", "X"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>["S", "X"]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>742056710653476</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0012.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0012.json</t>
+      <c r="K5" t="n">
+        <v>975231564482028</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0003.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="216.75" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="6" ht="216.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks with values below 6.
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 13.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 13.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["F"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>["F"]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1831835478892593</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0017.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="216.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 7?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 7?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "Z"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>["B", "Z"]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2465055457828811</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0016.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="216.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 2.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -6054,63 +6374,63 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks with values below 6.
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 2.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["S", "X"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>["S", "X"]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>1077442909805690</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0021.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0021.json</t>
+      <c r="K8" t="n">
+        <v>3571995346554019</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0000.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0000.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="216.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="9" ht="216.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 19.
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 18?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -6118,63 +6438,127 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 19.
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 18?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "E", "F", "K", "V", "X", "Y"], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>["C", "E", "F", "K", "V", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "D", "J", "S", "T", "U", "V", "W", "Y"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["B", "D", "J", "S", "T", "U", "V", "W", "Y"]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1196487768936235</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0017.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0017.json</t>
+      <c r="K9" t="n">
+        <v>3579453067844686</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0021.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0021.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="216.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="10" ht="216.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 14?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 10.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 10.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "K", "T", "Z"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "K", "T", "Z"]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3707447673711748</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0010.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="216.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks have values lower than 13?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer field: set "answer" to the number of matching marks as an integer.
@@ -6182,63 +6566,255 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 14?
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks have values lower than 13?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E", "G", "M", "U"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["E", "G", "M", "U"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3884100202993408</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0020.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="216.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 5.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 5.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "X"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["B", "X"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4243719412941679</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0013.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="216.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 8?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. What number of labeled marks have values lower than 8?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "D", "E", "J", "M", "Q", "X", "Y"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "D", "E", "J", "M", "Q", "X", "Y"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4913125113261870</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0008.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="216.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 21.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 21.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["G", "K", "M", "W"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>["G", "K", "M", "W"]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "D", "E", "J", "N", "R", "T", "W"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "D", "E", "J", "N", "R", "T", "W"]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1447732221513834</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0006.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0006.json</t>
+      <c r="K14" t="n">
+        <v>5053127600023831</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0005.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0005.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="216.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="15" ht="216.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value less than 20?
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 48.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -6246,63 +6822,63 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value less than 20?
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 48.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "F", "H", "K", "P", "T", "V", "W", "Y"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>["B", "F", "H", "K", "P", "T", "V", "W", "Y"]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["K", "L", "M", "P", "V", "Y", "Z"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["K", "L", "M", "P", "V", "Y", "Z"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1512316678864260</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0010.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0010.json</t>
+      <c r="K15" t="n">
+        <v>5300380012441677</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0006.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="216.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="16" ht="216.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 3.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Find how many labeled marks are under 31.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -6310,63 +6886,63 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 3.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Find how many labeled marks are under 31.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
+Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [], "answer": 0}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["N", "R", "S", "T", "U", "Y", "Z"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["N", "R", "S", "T", "U", "Y", "Z"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1594702663232872</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0007.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0007.json</t>
+      <c r="K16" t="n">
+        <v>5395707623754450</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0012.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0012.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="216.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="17" ht="216.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks with values below 13.
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly less than 7.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer format: set "answer" to the number of matching marks as an integer.
@@ -6374,191 +6950,575 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks with values below 13.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks show values strictly less than 7.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "C", "F", "G", "H", "M", "P", "Q", "U"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>["A", "C", "F", "G", "H", "M", "P", "Q", "U"]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "D", "G", "P", "R", "U"], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>["A", "D", "G", "P", "R", "U"]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>2462569560815609</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0003.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0003.json</t>
+      <c r="K17" t="n">
+        <v>6181926689641614</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0019.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="216.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="18" ht="216.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks are under 21.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Find how many labeled marks are under 14.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
+Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks are under 21.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Find how many labeled marks are under 14.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["N"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["N"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6824512580586992</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0002.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="216.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value less than 17?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value less than 17?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["P", "Y"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["P", "Y"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7163430256174013</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0001.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="216.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Determine how many marks show values strictly less than 19.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Determine how many marks show values strictly less than 19.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["F", "H", "J", "Q", "R", "Z"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>["F", "H", "J", "Q", "R", "Z"]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "D", "G", "H", "K", "R", "X"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["C", "D", "G", "H", "K", "R", "X"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2517059059382483</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0008.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0008.json</t>
+      <c r="K20" t="n">
+        <v>7183785167241787</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0018.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0018.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="216.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="21" ht="216.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values lower than 11?
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value less than 2?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks have values lower than 11?
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value less than 2?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["E", "G"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["E", "G"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7270049679101044</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0014.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="216.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 20.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Count the labeled marks with values below 20.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "D", "K", "Q", "U"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["C", "D", "K", "Q", "U"]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7407205368710325</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0011.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="216.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 15.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks with values below 15.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["J"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>["J"]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "U", "W"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "U", "W"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>2537411629319486</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0004.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0004.json</t>
+      <c r="K23" t="n">
+        <v>7667735111906742</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0024.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0024.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="216.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="24" ht="216.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>below_threshold</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 19.
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value less than 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value less than 2?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "H", "L", "N", "P", "S"], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["B", "H", "L", "N", "P", "S"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7676075561630452</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0022.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="216.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Determine how many marks show values strictly less than 2.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["A","M"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Determine how many marks show values strictly less than 2.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["T"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["T"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>8425717884154055</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0007.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="216.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>below_threshold</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 19?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -6566,1006 +7526,46 @@
 {"evidence":["A","M"],"answer":2}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 19.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["E", "P"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>["E", "P"]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2667135005208838</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0002.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="216.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks have values lower than 8?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks have values lower than 8?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "N", "Z"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>["B", "N", "Z"]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2903429331583974</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0024.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="216.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 20?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 20?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "D", "E"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>["B", "D", "E"]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3665251068338056</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0016.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="216.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 6.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks show values strictly less than 6.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [], "answer": 0}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4128095823358516</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0023.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="216.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value less than 21?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value less than 21?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "F", "K", "M", "Q", "R", "V", "W", "X", "Z"], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>["C", "F", "K", "M", "Q", "R", "V", "W", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4587172959106606</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0001.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks show values strictly less than 17.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks show values strictly less than 17.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "D", "E", "L", "M", "Q", "T", "V"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "D", "E", "L", "M", "Q", "T", "V"]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4958179568562675</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0014.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="216.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Determine how many marks show values strictly less than 20.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Determine how many marks show values strictly less than 20.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "V", "X"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>["B", "V", "X"]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5250617005719703</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0009.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="216.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks have values lower than 2?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks have values lower than 2?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [], "answer": 0}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5433631681325817</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0018.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="216.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value less than 18?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value less than 18?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "E", "H", "L", "N", "P", "S", "Y", "Z"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>["B", "E", "H", "L", "N", "P", "S", "Y", "Z"]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5503694285844305</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0011.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="216.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value less than 19?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value less than 19?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["K"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>["K"]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5638167101337084</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0022.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="216.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks have values lower than 9?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks have values lower than 9?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. What number of labeled marks have values lower than 19?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["K", "S"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>["K", "S"]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "D", "F", "P", "Q", "R"], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>["B", "D", "F", "P", "Q", "R"]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>6276222026501370</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0013.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="216.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Find how many labeled marks are under 13.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Find how many labeled marks are under 13.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "E", "J", "L", "N", "R", "S", "Z"], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>["C", "E", "J", "L", "N", "R", "S", "Z"]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>6482176638201218</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0015.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="216.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values below 8.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values below 8.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["L", "T", "X", "Y"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>["L", "T", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6556491956613792</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0019.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="216.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 21.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 21.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "D", "H", "L", "S", "T", "W", "X", "Z"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>["C", "D", "H", "L", "S", "T", "W", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7287275070153227</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0000.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="216.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 20.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Count the labeled marks with values below 20.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "D", "K", "P", "Q", "S", "W", "Y"], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>["B", "D", "K", "P", "Q", "S", "W", "Y"]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>7334199308698374</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0005.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="216.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>below_threshold</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values below 24.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values less than the threshold.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["A","M"],"answer":2}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. Count the labeled marks with values below 24.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":2}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["D", "E", "K", "T", "X", "Y"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>["D", "E", "K", "T", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>7459232644440767</v>
+        <v>8844773921346992</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/below_threshold/0020.png</t>
+          <t>charts/task_charts_counting_value_count/images/below_threshold/0004.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/below_threshold/0020.json</t>
+          <t>charts/task_charts_counting_value_count/data/below_threshold/0004.json</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,391 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [7, 76]?
+          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value in the inclusive interval [2, 8]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value in the inclusive interval [2, 8]?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D", "E", "G", "H", "J", "R", "V"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>["D", "E", "G", "H", "J", "R", "V"]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>518276298030924</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0024.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="216.75" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Find how many labeled marks have values from 2 to 20, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Find how many labeled marks have values from 2 to 20, inclusive.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["Y"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>["Y"]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>876672578322305</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0003.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="216.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [4, 40]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [4, 40]?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "M", "N"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>["B", "M", "N"]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1425523507532378</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0019.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="216.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 5 to 20, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 5 to 20, inclusive.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "F", "H", "J", "M", "Q", "S", "X", "Y"], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "F", "H", "J", "M", "Q", "S", "X", "Y"]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1659418453645651</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0015.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="216.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value in the inclusive interval [1, 64]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. How many labeled marks have value in the inclusive interval [1, 64]?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "C", "W", "X", "Z"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>["A", "C", "W", "X", "Z"]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2198323910298549</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0017.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="216.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [15, 17]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [15, 17]?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["R"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>["R"]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2283479453201596</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0018.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="216.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. What number of labeled marks lie in the inclusive interval [1, 4]?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer field: set "answer" to the number of matching marks as an integer.
@@ -7687,63 +8071,191 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [7, 76]?
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. What number of labeled marks lie in the inclusive interval [1, 4]?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "D", "X"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>["A", "D", "X"]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "J", "L", "X"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>["A", "J", "L", "X"]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>236805178715784</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0008.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0008.json</t>
+      <c r="K8" t="n">
+        <v>2360281599152714</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0006.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="216.75" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="9" ht="216.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks lie in the inclusive interval [1, 14]?
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value in the inclusive interval [16, 17]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. How many labeled marks have value in the inclusive interval [16, 17]?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["G", "K", "L", "Z"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["G", "K", "L", "Z"]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2451635077100581</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0004.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="216.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks lie in the inclusive interval [1, 10]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. What number of labeled marks lie in the inclusive interval [1, 10]?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "F", "G"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "F", "G"]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3324755979072663</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0013.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="216.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 20]?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -7751,63 +8263,319 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. What number of labeled marks lie in the inclusive interval [1, 14]?
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 20]?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
+Answer: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["H", "J", "K", "N"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>["H", "J", "K", "N"]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "D", "L", "M", "Q", "S", "U", "W", "Z"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["B", "D", "L", "M", "Q", "S", "U", "W", "Z"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>782832125822506</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0016.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0016.json</t>
+      <c r="K11" t="n">
+        <v>3385271495109182</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0008.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="216.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="12" ht="216.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks whose values fall in [1, 11], inclusive.
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks have values from 1 to 13, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks have values from 1 to 13, inclusive.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "E", "J", "L", "N", "U", "Z"], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["B", "E", "J", "L", "N", "U", "Z"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4059177506419853</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0000.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="216.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 0 and 85, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 0 and 85, inclusive.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "C", "J", "L", "M"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["A", "C", "J", "L", "M"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4168384763776753</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0023.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="216.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 1 and 4, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 1 and 4, inclusive.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D", "N", "S", "Y"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>["D", "N", "S", "Y"]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4450653383415388</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0007.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="216.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [5, 20]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [5, 20]?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "E", "J", "K", "Q", "S", "X", "Y"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "E", "J", "K", "Q", "S", "X", "Y"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4638236879612557</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0022.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="216.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 1 to 15, inclusive.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer requirement: set "answer" to the number of matching marks as an integer.
@@ -7815,63 +8583,63 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Read the chart values and count the matching marks. Count the labeled marks whose values fall in [1, 11], inclusive.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 1 to 15, inclusive.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
+Answer field: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "J", "K", "L", "T"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>["A", "J", "K", "L", "T"]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["H", "M", "R"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["H", "M", "R"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1342451323956769</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0003.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0003.json</t>
+      <c r="K16" t="n">
+        <v>6490415675401562</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0014.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="216.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="17" ht="216.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks have values between 14 and 17, inclusive.
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [13, 15], inclusive.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer: set "answer" to the number of matching marks as an integer.
@@ -7879,63 +8647,63 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks have values between 14 and 17, inclusive.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [13, 15], inclusive.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "F", "M", "Q", "V", "Z"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>["C", "F", "M", "Q", "V", "Z"]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "E", "M"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>["C", "E", "M"]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1520151667376933</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0021.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0021.json</t>
+      <c r="K17" t="n">
+        <v>6560249070753526</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0002.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0002.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="216.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="18" ht="216.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Find how many labeled marks have values from 11 to 20, inclusive.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [19, 19]?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer field: set "answer" to the number of matching marks as an integer.
@@ -7943,63 +8711,447 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled horizontal bar chart. Each bar's numeric length can be read from the horizontal axis. Read the chart values and count the matching marks. Find how many labeled marks have values from 11 to 20, inclusive.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [19, 19]?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "C", "D", "J", "K", "L", "P", "Q"], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>["A", "C", "D", "J", "K", "L", "P", "Q"]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1883537716652255</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0019.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0019.json</t>
+      <c r="K18" t="n">
+        <v>6949274286702298</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0020.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="216.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="19" ht="216.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [15, 17]?
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 84]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer format: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 84]?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "F", "L", "P", "Q", "S", "X", "Z"], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["B", "F", "L", "P", "Q", "S", "X", "Z"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7663182001358826</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0009.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="216.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 5]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. How many labeled marks have value in the inclusive interval [1, 5]?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "C", "G", "H", "M", "R", "S", "U", "Z"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["A", "C", "G", "H", "M", "R", "S", "U", "Z"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>7707451639006869</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0011.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="216.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Determine how many marks have values between 31 and 68, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Read the chart values and count the matching marks. Determine how many marks have values between 31 and 68, inclusive.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "D"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["B", "D"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8055282463093259</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0010.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="216.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Determine how many marks have values between 0 and 59, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Use the chart values to answer the counting question. Determine how many marks have values between 0 and 59, inclusive.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "E", "H", "M", "P", "S", "Z"], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "E", "H", "M", "P", "S", "Z"]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8207519573947203</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0016.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="216.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [1, 20]?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [1, 20]?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "E", "G", "J", "K", "M", "Q", "R", "X", "Y"], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["A", "E", "G", "J", "K", "M", "Q", "R", "X", "Y"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>8412219117161068</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0005.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="216.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks have values between 15 and 19, inclusive.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
+Answer: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"evidence":["C","F","Q"],"answer":3}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Count the labeled marks that satisfy the requested value condition. Determine how many marks have values between 15 and 19, inclusive.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the number of matching marks as an integer.
+Example JSON:
+{"answer":3}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["F", "H", "K", "L", "N", "S", "V", "X", "Z"], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["F", "H", "K", "L", "N", "S", "V", "X", "Z"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>8508323612974651</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0012.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="216.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_charts_counting_value_count</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>in_interval</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [12, 20], inclusive.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -8007,63 +9159,63 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [15, 17]?
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [12, 20], inclusive.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
+Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "E", "F", "H"], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>["A", "E", "F", "H"]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["F", "G", "L", "Z"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["F", "G", "L", "Z"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>2340660999777547</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0006.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0006.json</t>
+      <c r="K25" t="n">
+        <v>8868463745720414</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0001.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="216.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="26" ht="216.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_charts_counting_value_count</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>in_interval</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks have values between 7 and 98, inclusive.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value in the inclusive interval [5, 20]?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
 Answer rule: set "answer" to the number of matching marks as an integer.
@@ -8071,1198 +9223,46 @@
 {"evidence":["C","F","Q"],"answer":3}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Count the labeled marks that satisfy the requested value condition. Determine how many marks have values between 7 and 98, inclusive.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["E", "M"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>["E", "M"]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2426962184038534</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0001.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="216.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [16, 16]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled lollipop chart. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. What number of labeled marks lie in the inclusive interval [16, 16]?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value in the inclusive interval [5, 20]?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the number of matching marks as an integer.
 Example JSON:
 {"answer":3}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [], "answer": 0}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "L", "N", "P", "R", "V", "X", "Y"], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>["C", "L", "N", "P", "R", "V", "X", "Y"]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2595800790706737</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0022.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="216.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Determine how many marks have values between 4 and 20, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Determine how many marks have values between 4 and 20, inclusive.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "D"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>["B", "D"]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3347459302751423</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0024.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="216.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 13 to 15, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Find how many labeled marks have values from 13 to 15, inclusive.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["T", "U"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>["T", "U"]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3424476419096767</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0000.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="216.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. What number of labeled marks lie in the inclusive interval [5, 85]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a donut chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Answer this question. What number of labeled marks lie in the inclusive interval [5, 85]?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "G", "H", "N", "T", "X"], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>["B", "G", "H", "N", "T", "X"]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3796258073886347</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0015.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="216.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [8, 12], inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled line chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [8, 12], inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "Q", "T", "W", "X"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>["A", "Q", "T", "W", "X"]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3810767739702184</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0007.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="216.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Answer this question. How many labeled marks have value in the inclusive interval [5, 20]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Answer this question. How many labeled marks have value in the inclusive interval [5, 20]?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["G"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>["G"]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4187404935364671</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0009.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="216.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [1, 92]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. How many labeled marks have value in the inclusive interval [1, 92]?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "H", "K", "L", "M", "R", "Z"], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "H", "K", "L", "M", "R", "Z"]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4526878717260367</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0013.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 37 and 56, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a pie chart with differently colored slices. A legend on the right maps each slice color to its label, and the relevant values are the percentages printed on the slices. Determine how many labeled marks meet the stated value condition. Determine how many marks have values between 37 and 56, inclusive.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["N"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>["N"]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4752423313437559</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0004.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="216.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Determine how many marks have values between 1 and 14, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Use the chart values to answer the counting question. Determine how many marks have values between 1 and 14, inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["V", "Z"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>["V", "Z"]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5135012723634478</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0014.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="216.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Count the labeled marks whose values fall in [15, 20], inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Answer this question. Count the labeled marks whose values fall in [15, 20], inclusive.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["P", "T", "Y"], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>["P", "T", "Y"]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5198529532178342</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0017.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="216.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [15, 20], inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled bar chart. Each bar's numeric height can be read from the vertical axis. Use the chart values to answer the counting question. Count the labeled marks whose values fall in [15, 20], inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "G", "K", "T", "W", "X", "Z"], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>["C", "G", "K", "T", "W", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5205404840248309</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0023.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="216.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [11, 18]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Read the chart values and count the matching marks. How many labeled marks have value in the inclusive interval [11, 18]?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["N", "Q"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>["N", "Q"]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5365144582894538</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0020.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="216.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Answer this question. How many labeled marks have value in the inclusive interval [1, 14]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Answer this question. How many labeled marks have value in the inclusive interval [1, 14]?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "G", "H", "L", "R", "T"], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "G", "H", "L", "R", "T"]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>5373779002274832</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0018.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="216.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value in the inclusive interval [1, 18]?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer rule: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. How many labeled marks have value in the inclusive interval [1, 18]?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["Q"], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>["Q"]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>5711883126604448</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0010.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="216.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks whose values fall in [11, 11], inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled chart shown in the image: a labeled dot plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Count the labeled marks whose values fall in [11, 11], inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [], "answer": 0}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6495073643933020</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0011.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="216.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks have values from 12 to 13, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>You are given a labeled chart: a labeled area chart with visible point markers. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Count the labeled marks that satisfy the requested value condition. Find how many labeled marks have values from 12 to 13, inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["C", "E", "M", "Q", "R", "T", "U", "X", "Y"], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>["C", "E", "M", "Q", "R", "T", "U", "X", "Y"]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>6565289556126381</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0012.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="216.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. Count the labeled marks whose values fall in [1, 19], inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the chart in the image. It shows a labeled radar chart with one spoke per label. Each label marks one plotted point on the radar polygon, and the relevant values are the printed values near those points. Count the labeled marks that satisfy the requested value condition. Count the labeled marks whose values fall in [1, 19], inclusive.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["A", "H", "K", "L", "M", "N", "Z"], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>["A", "H", "K", "L", "M", "N", "Z"]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8431573021853161</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/images/in_interval/0005.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count/data/in_interval/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="216.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_charts_counting_value_count</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>in_interval</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks have values between 8 and 18, inclusive.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all marks with values in the inclusive interval.
-Answer field: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"evidence":["C","F","Q"],"answer":3}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the chart in the image. It shows a labeled scatter plot. Each label marks one plotted point, and the relevant values are the points' y-values on the vertical axis. Answer this question. Determine how many marks have values between 8 and 18, inclusive.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the number of matching marks as an integer.
-Example JSON:
-{"answer":3}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["N", "Q", "S", "X", "Z"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>["N", "Q", "S", "X", "Z"]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>label_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8911710480357126</v>
+        <v>8983815821940809</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/images/in_interval/0002.png</t>
+          <t>charts/task_charts_counting_value_count/images/in_interval/0021.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_charts_counting_value_count/data/in_interval/0002.json</t>
+          <t>charts/task_charts_counting_value_count/data/in_interval/0021.json</t>
         </is>
       </c>
     </row>
